--- a/data_preparation/data/argentina/df_integrated_jug_no_encontrados.xlsx
+++ b/data_preparation/data/argentina/df_integrated_jug_no_encontrados.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H140"/>
+  <dimension ref="A1:H157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,12 +477,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>herrera marcelo</t>
+          <t>roffo manuel</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>river plate</t>
+          <t>instituto</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -497,12 +497,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>meli juan andres</t>
+          <t>franco juan</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>godoy cruz</t>
+          <t>instituto</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -517,12 +517,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>leyes sosa bruno</t>
+          <t>mosevich leonel</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>godoy cruz</t>
+          <t>instituto</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -537,12 +537,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>domina jerome</t>
+          <t>alarcon fernando</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>union santa fe</t>
+          <t>instituto</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -557,12 +557,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pereyra fabio jesus</t>
+          <t>corda sebastian</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>central cordoba</t>
+          <t>instituto</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -577,12 +577,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>losada nahuel</t>
+          <t>graciani gabriel</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>instituto</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -597,12 +597,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>barinaga juan</t>
+          <t>linares nicolas</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>instituto</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -617,12 +617,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rebola alejandro</t>
+          <t>lodico gaston</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>instituto</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -637,12 +637,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>meriano nicolas</t>
+          <t>watson franco</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>instituto</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -657,12 +657,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ibacache matias</t>
+          <t>rodriguez santiago</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>instituto</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -677,12 +677,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pereira guillermo fabian</t>
+          <t>martinez adrian emmanuel</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>instituto</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -697,12 +697,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>longo santiago</t>
+          <t>garcia roberto</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>velez sarsfield</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -717,12 +717,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sanchez ulises</t>
+          <t>velazquez ramos gustavo</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>newell s</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -737,12 +737,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>hesar ibrahim</t>
+          <t>fernandez ignacio</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>boca juniors</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -757,12 +757,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>zapelli bruno</t>
+          <t>barcia mateo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>independiente</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -777,12 +777,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>vegetti pablo</t>
+          <t>baez cristian</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>independiente</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -797,12 +797,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pena biafore felipe</t>
+          <t>costa ayrton enrique</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>arsenal sarandi</t>
+          <t>independiente</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -817,12 +817,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>muscia gonzalo emanuel</t>
+          <t>meli juan andres</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>arsenal sarandi</t>
+          <t>godoy cruz</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -837,12 +837,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bedoya flabian</t>
+          <t>leyes sosa bruno</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>arsenal sarandi</t>
+          <t>godoy cruz</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -857,12 +857,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>estigarribia marcelo luciano</t>
+          <t>domina jerome</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>atletico  tucuman</t>
+          <t>union santa fe</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -877,12 +877,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>baez cristian</t>
+          <t>pereyra fabio jesus</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>independiente</t>
+          <t>central cordoba</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -897,12 +897,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>costa ayrton enrique</t>
+          <t>losada nahuel</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>independiente</t>
+          <t>belgrano</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -917,12 +917,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>mamut leandro</t>
+          <t>barinaga juan</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gimnasia la plata</t>
+          <t>belgrano</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -937,12 +937,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>roffo manuel</t>
+          <t>rebola alejandro</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>instituto</t>
+          <t>belgrano</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>franco juan</t>
+          <t>meriano nicolas</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>instituto</t>
+          <t>belgrano</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -977,12 +977,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mosevich leonel</t>
+          <t>ibacache matias</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>instituto</t>
+          <t>belgrano</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -997,12 +997,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>alarcon fernando</t>
+          <t>pereira guillermo fabian</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>instituto</t>
+          <t>belgrano</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -1017,12 +1017,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>corda sebastian</t>
+          <t>longo santiago</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>instituto</t>
+          <t>belgrano</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -1037,12 +1037,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>graciani gabriel</t>
+          <t>sanchez ulises</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>instituto</t>
+          <t>belgrano</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -1057,12 +1057,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>linares nicolas</t>
+          <t>hesar ibrahim</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>instituto</t>
+          <t>belgrano</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -1077,12 +1077,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cuello braian</t>
+          <t>zapelli bruno</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>instituto</t>
+          <t>belgrano</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -1097,12 +1097,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>lodico gaston</t>
+          <t>vegetti pablo</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>instituto</t>
+          <t>belgrano</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -1117,12 +1117,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>rodriguez santiago</t>
+          <t>pena biafore felipe</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>instituto</t>
+          <t>arsenal sarandi</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -1137,12 +1137,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>martinez adrian emmanuel</t>
+          <t>muscia gonzalo emanuel</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>instituto</t>
+          <t>arsenal sarandi</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -1157,12 +1157,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>figal jorge</t>
+          <t>bedoya flabian</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>boca juniors</t>
+          <t>arsenal sarandi</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -1177,12 +1177,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>velazquez ramos gustavo</t>
+          <t>quiros santiago</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>newell s</t>
+          <t>racing club</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -1197,12 +1197,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>mansilla zahir facundo</t>
+          <t>vera gabriel</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>newell s</t>
+          <t>argentinos juniors</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -1217,12 +1217,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>portillo marcos</t>
+          <t>herrera marcelo</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>newell s</t>
+          <t>river plate</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -1237,12 +1237,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>serrizuela juan pablo</t>
+          <t>estigarribia marcelo luciano</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>barracas central</t>
+          <t>atletico  tucuman</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
@@ -1257,12 +1257,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>farias franco</t>
+          <t>mamut leandro</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>barracas central</t>
+          <t>gimnasia la plata</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
@@ -1277,12 +1277,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>tolosa franco</t>
+          <t>cuello braian</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>barracas central</t>
+          <t>instituto</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
@@ -1297,12 +1297,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>aguilar caraballo brian mauricio</t>
+          <t>figal jorge</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>lanus</t>
+          <t>boca juniors</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
@@ -1317,12 +1317,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>aranda pablo</t>
+          <t>mansilla zahir facundo</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>lanus</t>
+          <t>newell s</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
@@ -1337,12 +1337,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>echeverri claudio</t>
+          <t>portillo marcos</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>river plate</t>
+          <t>newell s</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
@@ -1357,12 +1357,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>altamira facundo</t>
+          <t>bay jonathan</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>godoy cruz</t>
+          <t>instituto</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
@@ -1377,12 +1377,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>rivamar enzo</t>
+          <t>carranza jorge</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>godoy cruz</t>
+          <t>instituto</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
@@ -1397,12 +1397,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>galdames thomas ignacio</t>
+          <t>cerato giuliano</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>godoy cruz</t>
+          <t>instituto</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
@@ -1417,12 +1417,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>salvareschi braian</t>
+          <t>garrido oscar</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>godoy cruz</t>
+          <t>instituto</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -1437,12 +1437,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>goyeneche juan</t>
+          <t>parnisiari ezequiel</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>san lorenzo</t>
+          <t>instituto</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
@@ -1457,12 +1457,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>lujan melli gonzalo</t>
+          <t>rodriguez gregorio</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>san lorenzo</t>
+          <t>instituto</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
@@ -1477,12 +1477,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>peruzii francesco</t>
+          <t>varela joaquin</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>san lorenzo</t>
+          <t>instituto</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
@@ -1497,12 +1497,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>castillon gomez bryan david</t>
+          <t>watson nicolas</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>union santa fe</t>
+          <t>instituto</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
@@ -1517,12 +1517,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>mosqueira marcos</t>
+          <t>rodriguez axel</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>union santa fe</t>
+          <t>instituto</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
@@ -1537,12 +1537,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>venetucci valentino</t>
+          <t>bochi roberto</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>union santa fe</t>
+          <t>instituto</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
@@ -1557,12 +1557,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>vera santino</t>
+          <t>barrientos nicolas</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>racing club</t>
+          <t>instituto</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
@@ -1577,12 +1577,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>quiros santiago</t>
+          <t>bertolo nicolas</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>racing club</t>
+          <t>banfield</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
@@ -1597,12 +1597,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>rodriguez baltasar</t>
+          <t>rivera geronimo</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>racing club</t>
+          <t>banfield</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
@@ -1617,12 +1617,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>perez tomas</t>
+          <t>goyeneche juan</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>racing club</t>
+          <t>san lorenzo</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
@@ -1637,12 +1637,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>cansinos ramon</t>
+          <t>lujan melli gonzalo</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>central cordoba</t>
+          <t>san lorenzo</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
@@ -1657,12 +1657,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>vasquez diego</t>
+          <t>peruzii francesco</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>central cordoba</t>
+          <t>san lorenzo</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
@@ -1677,12 +1677,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>quintero valentino</t>
+          <t>alvarez fabio</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>rosario central</t>
+          <t>talleres</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
@@ -1697,12 +1697,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>o connor tomas</t>
+          <t>olmos tomas</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>rosario central</t>
+          <t>talleres</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
@@ -1717,12 +1717,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>toledo alejo</t>
+          <t>alvez maximiliano</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>rosario central</t>
+          <t>talleres</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
@@ -1737,12 +1737,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>amaya andres</t>
+          <t>carrasco julian</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>boca juniors</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
@@ -1757,12 +1757,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>barrea daniel</t>
+          <t>di lollo lautaro</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>boca juniors</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
@@ -1777,12 +1777,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>bordagaray fabian</t>
+          <t>genez nahuel</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>boca juniors</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
@@ -1797,12 +1797,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>jara franco</t>
+          <t>rodriguez roman</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>boca juniors</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
@@ -1817,12 +1817,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>novaretti diego</t>
+          <t>rolon esteban</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>boca juniors</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -1837,12 +1837,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>susvielles joaquin</t>
+          <t>anselmino aaron</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>boca juniors</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -1857,12 +1857,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>vicentini manuel</t>
+          <t>cortes brandon</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>boca juniors</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
@@ -1877,12 +1877,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ramirez ivan</t>
+          <t>ramirez pablo</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>platense</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
@@ -1897,12 +1897,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>compagnucci gabriel</t>
+          <t>toledo pacheco lautaro</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>platense</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -1917,12 +1917,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>diarte lucas</t>
+          <t>monje alejo pablo</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>platense</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -1937,12 +1937,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>rojas ariel</t>
+          <t>lopez santiago</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>independiente</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -1957,12 +1957,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>castro tomas</t>
+          <t>martinez david</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>independiente</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -1977,12 +1977,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>cardozo juan</t>
+          <t>ostachuk javier patricio</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>argentinos juniors</t>
+          <t>independiente</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -1997,12 +1997,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>vera gabriel</t>
+          <t>atencio rodrigo</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>argentinos juniors</t>
+          <t>independiente</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -2017,12 +2017,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>espindola matias</t>
+          <t>serrizuela juan pablo</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>tigre</t>
+          <t>barracas central</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -2037,12 +2037,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>palavecino agustin</t>
+          <t>farias franco</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>estudiantes</t>
+          <t>barracas central</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -2057,12 +2057,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>cougo ayrton</t>
+          <t>tolosa franco</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>sarmiento</t>
+          <t>barracas central</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -2077,12 +2077,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>garnier luis</t>
+          <t>aguilar caraballo brian mauricio</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>sarmiento</t>
+          <t>lanus</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
@@ -2097,12 +2097,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ciccioli ulises</t>
+          <t>aranda pablo</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>rosario central</t>
+          <t>lanus</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
@@ -2117,12 +2117,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>alanis maximiliano</t>
+          <t>altamira facundo</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>atletico  tucuman</t>
+          <t>godoy cruz</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -2137,12 +2137,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>atencio rodrigo</t>
+          <t>rivamar enzo</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>independiente</t>
+          <t>godoy cruz</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -2157,12 +2157,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>lopez santiago</t>
+          <t>galdames thomas ignacio</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>independiente</t>
+          <t>godoy cruz</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -2177,12 +2177,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ostachuk javier patricio</t>
+          <t>salvareschi braian</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>independiente</t>
+          <t>godoy cruz</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -2197,12 +2197,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>martinez david</t>
+          <t>castillon gomez bryan david</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>independiente</t>
+          <t>union santa fe</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -2217,12 +2217,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>barcia mateo</t>
+          <t>mosqueira marcos</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>independiente</t>
+          <t>union santa fe</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -2237,12 +2237,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>galvan tomas ezequiel</t>
+          <t>venetucci valentino</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>colon</t>
+          <t>union santa fe</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -2257,12 +2257,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>neris pablo</t>
+          <t>vera santino</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>colon</t>
+          <t>racing club</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -2277,12 +2277,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>gonzalo gonzalez</t>
+          <t>rodriguez baltasar</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>gimnasia la plata</t>
+          <t>racing club</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -2297,12 +2297,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>palazzo bruno</t>
+          <t>perez tomas</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>gimnasia la plata</t>
+          <t>racing club</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -2317,12 +2317,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>sanchez nicolas</t>
+          <t>cansinos ramon</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>gimnasia la plata</t>
+          <t>central cordoba</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -2337,12 +2337,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>mammini ivo</t>
+          <t>vasquez diego</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>gimnasia la plata</t>
+          <t>central cordoba</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -2357,12 +2357,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>torres franco</t>
+          <t>quintero valentino</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>gimnasia la plata</t>
+          <t>rosario central</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -2377,12 +2377,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>cocimano sebastian</t>
+          <t>o connor tomas</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>gimnasia la plata</t>
+          <t>rosario central</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -2397,12 +2397,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>di luciano ramiro</t>
+          <t>toledo alejo</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>banfield</t>
+          <t>rosario central</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
@@ -2417,12 +2417,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>rivera geronimo</t>
+          <t>amaya andres</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>banfield</t>
+          <t>belgrano</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
@@ -2437,12 +2437,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>benitez angel</t>
+          <t>barrea daniel</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>huracan</t>
+          <t>belgrano</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
@@ -2457,12 +2457,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>martinez alexis</t>
+          <t>bordagaray fabian</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>huracan</t>
+          <t>belgrano</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
@@ -2477,12 +2477,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>albertengo lucas</t>
+          <t>jara franco</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>instituto</t>
+          <t>belgrano</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
@@ -2497,12 +2497,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>barrientos nicolas</t>
+          <t>novaretti diego</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>instituto</t>
+          <t>belgrano</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
@@ -2517,12 +2517,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>bilbao emanuel</t>
+          <t>susvielles joaquin</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>instituto</t>
+          <t>belgrano</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
@@ -2537,12 +2537,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>bochi roberto</t>
+          <t>vicentini manuel</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>instituto</t>
+          <t>belgrano</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
@@ -2557,12 +2557,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>parnisiari ezequiel</t>
+          <t>ramirez ivan</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>instituto</t>
+          <t>belgrano</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
@@ -2577,12 +2577,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>rodriguez gregorio</t>
+          <t>compagnucci gabriel</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>instituto</t>
+          <t>belgrano</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
@@ -2597,12 +2597,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>varela joaquin</t>
+          <t>diarte lucas</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>instituto</t>
+          <t>belgrano</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
@@ -2617,12 +2617,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>watson franco</t>
+          <t>rojas ariel</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>instituto</t>
+          <t>belgrano</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
@@ -2637,12 +2637,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>watson nicolas</t>
+          <t>castro tomas</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>instituto</t>
+          <t>belgrano</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
@@ -2657,12 +2657,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>cerato giuliano</t>
+          <t>cardozo juan</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>instituto</t>
+          <t>argentinos juniors</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
@@ -2677,12 +2677,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>garrido oscar</t>
+          <t>espindola matias</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>instituto</t>
+          <t>tigre</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
@@ -2697,12 +2697,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>rodriguez axel</t>
+          <t>palavecino agustin</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>instituto</t>
+          <t>estudiantes</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
@@ -2717,12 +2717,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>pernicone patricio</t>
+          <t>cougo ayrton</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>velez sarsfield</t>
+          <t>sarmiento</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
@@ -2737,12 +2737,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>alvarez fabio</t>
+          <t>garnier luis</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>talleres</t>
+          <t>sarmiento</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
@@ -2757,12 +2757,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>barrera diego</t>
+          <t>leon roberto</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>talleres</t>
+          <t>racing club</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
@@ -2777,12 +2777,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>olmos tomas</t>
+          <t>echeverri claudio</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>talleres</t>
+          <t>river plate</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
@@ -2797,12 +2797,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>herrera franco</t>
+          <t>gomez jose amado</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>barracas central</t>
+          <t>central cordoba</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
@@ -2817,12 +2817,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>genez nahuel</t>
+          <t>olguin gino</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>boca juniors</t>
+          <t>central cordoba</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
@@ -2837,12 +2837,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>rolon esteban</t>
+          <t>cabrera ivan</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>boca juniors</t>
+          <t>arsenal sarandi</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
@@ -2857,12 +2857,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>fernandez ignacio</t>
+          <t>forclaz ezequiel</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>boca juniors</t>
+          <t>tigre</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
@@ -2877,12 +2877,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>rossi genaro</t>
+          <t>ciccioli ulises</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>newell s</t>
+          <t>rosario central</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
@@ -2897,12 +2897,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>sotelo david</t>
+          <t>alanis maximiliano</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>newell s</t>
+          <t>atletico  tucuman</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
@@ -2917,12 +2917,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>lopez lucas</t>
+          <t>galvan tomas ezequiel</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>barracas central</t>
+          <t>colon</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
@@ -2937,12 +2937,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>prado andres</t>
+          <t>neris pablo</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>barracas central</t>
+          <t>colon</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
@@ -2957,12 +2957,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>lopez elias sebastian</t>
+          <t>gonzalo gonzalez</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>river plate</t>
+          <t>gimnasia la plata</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
@@ -2977,12 +2977,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>martinez hector</t>
+          <t>palazzo bruno</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>river plate</t>
+          <t>gimnasia la plata</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
@@ -2997,12 +2997,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ulariaga silvio</t>
+          <t>sanchez nicolas</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>godoy cruz</t>
+          <t>gimnasia la plata</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
@@ -3017,12 +3017,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>oliver francisco</t>
+          <t>mammini ivo</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>gimnasia la plata</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
@@ -3037,12 +3037,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>tapia ignacio</t>
+          <t>torres franco</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>belgrano</t>
+          <t>gimnasia la plata</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
@@ -3057,12 +3057,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ambrogio lucas</t>
+          <t>cocimano sebastian</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>argentinos juniors</t>
+          <t>gimnasia la plata</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
@@ -3077,12 +3077,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>pineiro gonzalo augustin</t>
+          <t>di luciano ramiro</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>estudiantes</t>
+          <t>banfield</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
@@ -3097,12 +3097,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>arismendi jair</t>
+          <t>benitez angel</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>sarmiento</t>
+          <t>huracan</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
@@ -3117,12 +3117,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>rambert tomas</t>
+          <t>martinez alexis</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>independiente</t>
+          <t>huracan</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
@@ -3137,7 +3137,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>bay jonathan</t>
+          <t>albertengo lucas</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3157,7 +3157,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>carranza jorge</t>
+          <t>bilbao emanuel</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3177,7 +3177,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>cavanagh tomas</t>
+          <t>pernicone patricio</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3197,12 +3197,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>mastronicola bruno</t>
+          <t>barrera diego</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>barracas central</t>
+          <t>talleres</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
@@ -3217,12 +3217,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>zeballos oscar</t>
+          <t>herrera franco</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>boca juniors</t>
+          <t>barracas central</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
@@ -3237,7 +3237,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>campagnaro marco</t>
+          <t>rossi genaro</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3254,6 +3254,346 @@
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
     </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>sotelo david</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>newell s</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="n">
+        <v>45084</v>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>cavanagh tomas</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>velez sarsfield</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="n">
+        <v>45084</v>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>campagnaro marco</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>newell s</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="n">
+        <v>45084</v>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>zeballos oscar</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>boca juniors</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="n">
+        <v>45084</v>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>valdivia gonzalo</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>platense</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="n">
+        <v>45084</v>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>lopez lucas</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>barracas central</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="n">
+        <v>45084</v>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>prado andres</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>barracas central</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n">
+        <v>45084</v>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>ulariaga silvio</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>godoy cruz</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="n">
+        <v>45084</v>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>oliver francisco</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>belgrano</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="n">
+        <v>45084</v>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>tapia ignacio</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>belgrano</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="n">
+        <v>45084</v>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>ambrogio lucas</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>argentinos juniors</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="n">
+        <v>45084</v>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>pineiro gonzalo augustin</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>estudiantes</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="n">
+        <v>45084</v>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>arismendi jair</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>sarmiento</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="n">
+        <v>45084</v>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>lopez elias sebastian</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>river plate</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="n">
+        <v>45084</v>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>martinez hector</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>river plate</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="n">
+        <v>45084</v>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>rambert tomas</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>independiente</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v>45084</v>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>mastronicola bruno</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>barracas central</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="n">
+        <v>45084</v>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
